--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-18) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-18) Legacy.xlsx
@@ -645,19 +645,19 @@
         <v>1145858598</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1145858598</v>
+        <v>1151683598</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1145858598</v>
+        <v>1151683598</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0</v>
+        <v>5825000</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>100</v>
+        <v>100.5083524276178</v>
       </c>
     </row>
     <row r="8">

--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-18) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-18) Legacy.xlsx
@@ -645,19 +645,19 @@
         <v>1145858598</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1151683598</v>
+        <v>1145858598</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1151683598</v>
+        <v>1145858598</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>5825000</v>
+        <v>0</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>100.5083524276178</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">

--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-18) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-18) Legacy.xlsx
@@ -1149,19 +1149,19 @@
         <v>532966503</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>532966503</v>
+        <v>534030503</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>532966503</v>
+        <v>534030503</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0</v>
+        <v>1064000</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>100</v>
+        <v>100.1996373119156</v>
       </c>
     </row>
     <row r="26">
@@ -2241,19 +2241,19 @@
         <v>373421530</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>373421530</v>
+        <v>377271530</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>373421530</v>
+        <v>377271530</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>3850000</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>100</v>
+        <v>101.0310064339354</v>
       </c>
     </row>
     <row r="65">

--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-18) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-18) Legacy.xlsx
@@ -1149,19 +1149,19 @@
         <v>532966503</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>534030503</v>
+        <v>532966503</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>534030503</v>
+        <v>532966503</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1064000</v>
+        <v>0</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>100.1996373119156</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">

--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-18) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-18) Legacy.xlsx
@@ -2241,19 +2241,19 @@
         <v>373421530</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>377271530</v>
+        <v>373421530</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>377271530</v>
+        <v>373421530</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>3850000</v>
+        <v>0</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>101.0310064339354</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65">

--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-18) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-18) Legacy.xlsx
@@ -2241,19 +2241,19 @@
         <v>373421530</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>373421530</v>
+        <v>377271530</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>373421530</v>
+        <v>377271530</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>3850000</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>100</v>
+        <v>101.0310064339354</v>
       </c>
     </row>
     <row r="65">
